--- a/stories/arbres/ATOM-REL.AMI.001-05.xlsx
+++ b/stories/arbres/ATOM-REL.AMI.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Olivier est au parc avec papa. Le bac à sable est tiède. Olivier a un moule étoile. Iris est près du toboggan. Olivier veut jouer. Papa dit : tu peux inviter. Inviter, c'est demander. Olivier marche vers Iris. Il dit : tu veux jouer avec nous ? Iris secoue la tête. Iris dit : non. Olivier a le ventre un peu serré. Papa s'approche. Papa dit : on peut accepter un non. Accepter un non, c'est possible. Olivier dit : d'accord. Il retourne au bac. Il creuse un chemin. Le sable coule entre les doigts. Iris joue au toboggan. Olivier n'insiste pas. Papa dit : merci. Tu as su inviter. Tu as su accepter un non. Olivier souffle. Il pose l'étoile dans le sable. Papa reste au banc.</t>
+          <t>Olivier est au parc avec papa. Le bac à sable est tiède. Olivier a un moule étoile. Iris est près du toboggan. Olivier veut jouer. Tu peux inviter. Inviter, c'est demander. Olivier marche vers Iris. Tu veux jouer avec nous ? Iris secoue la tête. Non. Olivier a le ventre un peu serré. Papa s'approche. On peut accepter un non. Accepter un non, c'est possible. D'accord. Il retourne au bac. Il creuse un chemin. Le sable coule entre les doigts. Iris joue au toboggan. Olivier n'insiste pas. Merci. Tu as su inviter. Tu as su accepter un non. Olivier souffle. Il pose l'étoile dans le sable. Papa reste au banc.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,22 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Olivier est au parc avec papa. Le bac à sable est tiède. Olivier a un moule étoile. Iris est près du toboggan. Olivier veut jouer.
+papa|Tu peux inviter. Inviter, c'est demander.
+narrateur|Olivier marche vers Iris.
+narrateur|Tu veux jouer avec nous ?
+narrateur|Iris secoue la tête.
+copine|Non.
+narrateur|Olivier a le ventre un peu serré. Papa s'approche.
+papa|On peut accepter un non. Accepter un non, c'est possible.
+enfant-m|D'accord. Il retourne au bac. Il creuse un chemin.
+narrateur|Le sable coule entre les doigts. Iris joue au toboggan. Olivier n'insiste pas.
+papa|Merci. Tu as su inviter. Tu as su accepter un non.
+narrateur|Olivier souffle. Il pose l'étoile dans le sable. Papa reste au banc.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1497,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Iris dit non. Que fait Olivier ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1670,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Olivier a su inviter. Iris a dit non. Olivier a pu accepter un non. Papa est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1833,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Olivier range le moule. Papa se lève du banc.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +2000,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2040,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.AMI.001-05.xlsx
+++ b/stories/arbres/ATOM-REL.AMI.001-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1321,6 +1326,11 @@
 narrateur|Olivier souffle. Il pose l'étoile dans le sable. Papa reste au banc.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1504,6 +1514,7 @@
           <t>narrateur|Iris dit non. Que fait Olivier ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1675,6 +1686,7 @@
           <t>narrateur|Olivier a su inviter. Iris a dit non. Olivier a pu accepter un non. Papa est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1838,6 +1850,7 @@
           <t>narrateur|Olivier range le moule. Papa se lève du banc.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2005,6 +2018,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2023,7 +2037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2047,6 +2061,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2248,6 +2276,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.AMI.001-05.xlsx
+++ b/stories/arbres/ATOM-REL.AMI.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Olivier invite au bac à sable</t>
+          <t>L'étoile d'Amir</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Amir invite Mila avec son moule étoile. Mila dit non. Amir accepte et creuse un chemin avec papa.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Olivier est au parc avec papa. Le bac à sable est tiède. Olivier a un moule étoile. Iris est près du toboggan. Olivier veut jouer. Tu peux inviter. Inviter, c'est demander. Olivier marche vers Iris. Tu veux jouer avec nous ? Iris secoue la tête. Non. Olivier a le ventre un peu serré. Papa s'approche. On peut accepter un non. Accepter un non, c'est possible. D'accord. Il retourne au bac. Il creuse un chemin. Le sable coule entre les doigts. Iris joue au toboggan. Olivier n'insiste pas. Merci. Tu as su inviter. Tu as su accepter un non. Olivier souffle. Il pose l'étoile dans le sable. Papa reste au banc.</t>
+          <t>Des traces mouillées sèchent sur le chemin. Elles deviennent de plus en plus claires. La chaîne de la balançoire cliquette. Un platane jette une ombre ronde. Le banc sent encore la pluie. Le manteau de papa est plié dessus. Amir, tu as vu l'ombre ? Elle est ronde, papa. Oui. On va au bac. En ce moment, Amir tient un moule. Le moule a la forme d'une étoile. Le métal est un peu froid. Le sable du bac est tiède. Je veux une étoile. Une étoile dans le sable, d'accord. Mila est près du toboggan. Ses chaussures sont encore un peu mouillées. Elle touche la rampe lisse. Tu peux inviter. Inviter, c'est demander. Amir marche vers Mila. Tu veux jouer avec nous ? Mila secoue la tête. Non. Amir a le ventre un peu serré. L'étoile reste dans sa main. Papa s'approche. On peut accepter un non. Accepter un non, c'est possible. D'accord. Amir retourne au bac. Il creuse un petit chemin. Le sable coule entre ses doigts. Il est fin et un peu rêche. Tu creuses bien. Le chemin va à l'étoile. Oui. Un chemin tout doux. Mila monte au toboggan. La rampe fait un petit bruit. Amir accepte le non. Il pose l'étoile dans le sable. Merci. Tu as su inviter. Tu as su accepter un non. Elle a dit non. Un non, c'est possible. On finit le chemin ? Oui, papa. Une feuille tourne dans l'ombre. Le sable sent le soleil qui revient. Tu as fini ton chemin ? Oui. Bravo. Tu as fait du bon travail. Amir souffle un peu. L'étoile reste au milieu du bac.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,18 +1324,64 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Olivier est au parc avec papa. Le bac à sable est tiède. Olivier a un moule étoile. Iris est près du toboggan. Olivier veut jouer.
-papa|Tu peux inviter. Inviter, c'est demander.
-narrateur|Olivier marche vers Iris.
-narrateur|Tu veux jouer avec nous ?
-narrateur|Iris secoue la tête.
+          <t>narrateur|Des traces mouillées sèchent sur le chemin.
+narrateur|Elles deviennent de plus en plus claires.
+narrateur|La chaîne de la balançoire cliquette.
+narrateur|Un platane jette une ombre ronde.
+narrateur|Le banc sent encore la pluie.
+narrateur|Le manteau de papa est plié dessus.
+papa|Amir, tu as vu l'ombre ?
+enfant-m|Elle est ronde, papa.
+papa|Oui.
+papa|On va au bac.
+narrateur|En ce moment, Amir tient un moule.
+narrateur|Le moule a la forme d'une étoile.
+narrateur|Le métal est un peu froid.
+narrateur|Le sable du bac est tiède.
+enfant-m|Je veux une étoile.
+papa|Une étoile dans le sable, d'accord.
+narrateur|Mila est près du toboggan.
+narrateur|Ses chaussures sont encore un peu mouillées.
+narrateur|Elle touche la rampe lisse.
+papa|Tu peux inviter.
+papa|Inviter, c'est demander.
+narrateur|Amir marche vers Mila.
+enfant-m|Tu veux jouer avec nous ?
+narrateur|Mila secoue la tête.
 copine|Non.
-narrateur|Olivier a le ventre un peu serré. Papa s'approche.
-papa|On peut accepter un non. Accepter un non, c'est possible.
-enfant-m|D'accord. Il retourne au bac. Il creuse un chemin.
-narrateur|Le sable coule entre les doigts. Iris joue au toboggan. Olivier n'insiste pas.
-papa|Merci. Tu as su inviter. Tu as su accepter un non.
-narrateur|Olivier souffle. Il pose l'étoile dans le sable. Papa reste au banc.</t>
+narrateur|Amir a le ventre un peu serré.
+narrateur|L'étoile reste dans sa main.
+narrateur|Papa s'approche.
+papa|On peut accepter un non.
+papa|Accepter un non, c'est possible.
+enfant-m|D'accord.
+narrateur|Amir retourne au bac.
+narrateur|Il creuse un petit chemin.
+narrateur|Le sable coule entre ses doigts.
+narrateur|Il est fin et un peu rêche.
+papa|Tu creuses bien.
+enfant-m|Le chemin va à l'étoile.
+papa|Oui.
+papa|Un chemin tout doux.
+narrateur|Mila monte au toboggan.
+narrateur|La rampe fait un petit bruit.
+narrateur|Amir accepte le non.
+narrateur|Il pose l'étoile dans le sable.
+papa|Merci.
+papa|Tu as su inviter.
+papa|Tu as su accepter un non.
+enfant-m|Elle a dit non.
+papa|Un non, c'est possible.
+papa|On finit le chemin ?
+enfant-m|Oui, papa.
+narrateur|Une feuille tourne dans l'ombre.
+narrateur|Le sable sent le soleil qui revient.
+papa|Tu as fini ton chemin ?
+enfant-m|Oui.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Amir souffle un peu.
+narrateur|L'étoile reste au milieu du bac.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1355,7 +1413,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Iris dit non. Que fait Olivier ?</t>
+          <t>Mila dit non. Que fait Amir ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1511,10 +1569,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Iris dit non. Que fait Olivier ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Mila dit non.
+narrateur|Que fait Amir ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1539,7 +1597,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Olivier a su inviter. Iris a dit non. Olivier a pu accepter un non. Papa est là.</t>
+          <t>Amir a demandé. C'est inviter. Mila a dit non. Amir a accepté le non. Tu as su inviter. Tu as su accepter un non. Bravo, Amir. J'ai dit d'accord. Oui. Un non, c'est possible. L'étoile reste dans le sable. Le toboggan brille un peu. Tu as fini le chemin ? Oui, papa.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1683,10 +1741,22 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Olivier a su inviter. Iris a dit non. Olivier a pu accepter un non. Papa est là.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Amir a demandé.
+narrateur|C'est inviter.
+narrateur|Mila a dit non.
+narrateur|Amir a accepté le non.
+papa|Tu as su inviter.
+papa|Tu as su accepter un non.
+papa|Bravo, Amir.
+enfant-m|J'ai dit d'accord.
+papa|Oui.
+papa|Un non, c'est possible.
+narrateur|L'étoile reste dans le sable.
+narrateur|Le toboggan brille un peu.
+papa|Tu as fini le chemin ?
+enfant-m|Oui, papa.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1711,7 +1781,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Olivier range le moule. Papa se lève du banc.</t>
+          <t>Amir range le moule étoile. Un peu de sable tombe. Je le secoue. Papa se lève du banc. Le manteau sent encore la pluie. Il est lourd. Oui. On le met sur le bras. Tu prends ma main ? Oui. Ils quittent le bac. Les traces mouillées ont disparu.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1847,10 +1917,20 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Olivier range le moule. Papa se lève du banc.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Amir range le moule étoile.
+narrateur|Un peu de sable tombe.
+papa|Je le secoue.
+narrateur|Papa se lève du banc.
+narrateur|Le manteau sent encore la pluie.
+enfant-m|Il est lourd.
+papa|Oui.
+papa|On le met sur le bras.
+papa|Tu prends ma main ?
+enfant-m|Oui.
+narrateur|Ils quittent le bac.
+narrateur|Les traces mouillées ont disparu.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1875,7 +1955,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Amir a invité. Il a accepté un non. L'étoile reste dans le bac. Bravo, Amir. On rentre ? Oui. On rentre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2015,10 +2095,16 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Amir a invité.
+narrateur|Il a accepté un non.
+narrateur|L'étoile reste dans le bac.
+papa|Bravo, Amir.
+enfant-m|On rentre ?
+papa|Oui.
+papa|On rentre.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2037,7 +2123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2075,6 +2161,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.AMI.001-05.xlsx
+++ b/stories/arbres/ATOM-REL.AMI.001-05.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Des traces mouillées sèchent sur le chemin. Elles deviennent de plus en plus claires. La chaîne de la balançoire cliquette. Un platane jette une ombre ronde. Le banc sent encore la pluie. Le manteau de papa est plié dessus. Amir, tu as vu l'ombre ? Elle est ronde, papa. Oui. On va au bac. En ce moment, Amir tient un moule. Le moule a la forme d'une étoile. Le métal est un peu froid. Le sable du bac est tiède. Je veux une étoile. Une étoile dans le sable, d'accord. Mila est près du toboggan. Ses chaussures sont encore un peu mouillées. Elle touche la rampe lisse. Tu peux inviter. Inviter, c'est demander. Amir marche vers Mila. Tu veux jouer avec nous ? Mila secoue la tête. Non. Amir a le ventre un peu serré. L'étoile reste dans sa main. Papa s'approche. On peut accepter un non. Accepter un non, c'est possible. D'accord. Amir retourne au bac. Il creuse un petit chemin. Le sable coule entre ses doigts. Il est fin et un peu rêche. Tu creuses bien. Le chemin va à l'étoile. Oui. Un chemin tout doux. Mila monte au toboggan. La rampe fait un petit bruit. Amir accepte le non. Il pose l'étoile dans le sable. Merci. Tu as su inviter. Tu as su accepter un non. Elle a dit non. Un non, c'est possible. On finit le chemin ? Oui, papa. Une feuille tourne dans l'ombre. Le sable sent le soleil qui revient. Tu as fini ton chemin ? Oui. Bravo. Tu as fait du bon travail. Amir souffle un peu. L'étoile reste au milieu du bac.</t>
+          <t>Des traces mouillées sèchent sur le chemin. Elles deviennent de plus en plus claires. La chaîne de la balançoire cliquette. Un platane jette une ombre ronde. Le banc sent encore la pluie. Le manteau de papa est plié dessus. Amir, tu as vu l'ombre ? Elle est ronde, papa. Oui. On va au bac. En ce moment, Amir tient un moule. Le moule a la forme d'une étoile. Le métal est un peu froid. Le sable du bac est tiède. Je veux une étoile. Une étoile dans le sable, d'accord. Mila est près du toboggan. Ses chaussures sont encore un peu mouillées. Elle touche la rampe lisse. Tu peux inviter. Inviter, c'est demander. Amir marche vers Mila. Tu veux jouer avec nous ? Mila secoue la tête. Non. Amir a le ventre un peu serré. L'étoile reste dans sa main. Papa s'approche. On peut accepter un non. Accepter un non, c'est possible. D'accord. Amir retourne au bac. Il creuse un petit chemin. Le sable coule entre ses doigts. Il est fin et un peu rêche. Tu creuses bien. Le chemin va à l'étoile. Oui. Un chemin tout doux. Mila monte au toboggan. La rampe fait un petit bruit. Amir accepte le non. Il pose l'étoile dans le sable. Merci. Tu as su inviter. Tu as su accepter un non. Elle a dit non. Un non, c'est possible. On finit le chemin ? Oui, papa. Une feuille tourne dans l'ombre. Le sable sent le soleil qui revient. Tu as fini ton chemin ? Oui. Bravo. Amir souffle un peu. L'étoile reste au milieu du bac.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Olivier est au parc avec papa. Le bac à sable est tiède. Olivier a un moule étoile. Iris est près du toboggan. Olivier veut jouer. Papa dit : tu peux &lt;emphasis level="moderate"&gt;inviter&lt;/emphasis&gt;. Inviter, c'est demander. Olivier marche vers Iris. Il dit : tu veux jouer avec nous ? Iris secoue la tête. Iris dit : non. Olivier a le ventre un peu serré. Papa s'approche. Papa dit : on peut accepter un non. Accepter un non, c'est possible. Olivier dit : d'accord. Il retourne au bac. Il creuse un chemin. Le sable coule entre les doigts. Iris joue au toboggan. Olivier n'insiste pas. Papa dit : merci. Tu as su inviter. Tu as su accepter un non. Olivier souffle. Il pose l'étoile dans le sable. Papa reste au banc.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Des traces mouillées sèchent sur le chemin. Elles deviennent de plus en plus claires. La chaîne de la balançoire cliquette. Un platane jette une ombre ronde. Le banc sent encore la pluie. Le manteau de papa est plié dessus. Amir, tu as vu l'ombre ? Elle est ronde, papa. Oui. On va au bac. En ce moment, Amir tient un moule. Le moule a la forme d'une étoile. Le métal est un peu froid. Le sable du bac est tiède. Je veux une étoile. Une étoile dans le sable, d'accord. Mila est près du toboggan. Ses chaussures sont encore un peu mouillées. Elle touche la rampe lisse. Tu peux inviter. Inviter, c'est demander. Amir marche vers Mila. Tu veux jouer avec nous ? Mila secoue la tête. Non. Amir a le ventre un peu serré. L'étoile reste dans sa main. Papa s'approche. On peut accepter un non. Accepter un non, c'est possible. D'accord. Amir retourne au bac. Il creuse un petit chemin. Le sable coule entre ses doigts. Il est fin et un peu rêche. Tu creuses bien. Le chemin va à l'étoile. Oui. Un chemin tout doux. Mila monte au toboggan. La rampe fait un petit bruit. Amir accepte le non. Il pose l'étoile dans le sable. Merci. Tu as su inviter. Tu as su accepter un non. Elle a dit non. Un non, c'est possible. On finit le chemin ? Oui, papa. Une feuille tourne dans l'ombre. Le sable sent le soleil qui revient. Tu as fini ton chemin ? Oui. Bravo. Amir souffle un peu. L'étoile reste au milieu du bac.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1379,7 +1379,6 @@
 papa|Tu as fini ton chemin ?
 enfant-m|Oui.
 papa|Bravo.
-papa|Tu as fait du bon travail.
 narrateur|Amir souffle un peu.
 narrateur|L'étoile reste au milieu du bac.</t>
         </is>
@@ -1418,7 +1417,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Iris dit non. Que fait Olivier ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila dit non. Que fait Amir ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1602,7 +1601,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Olivier a su &lt;emphasis level="moderate"&gt;inviter&lt;/emphasis&gt;. Iris a dit non. Olivier a pu accepter un non. Papa est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir a demandé. C'est inviter. Mila a dit non. Amir a accepté le non. Tu as su inviter. Tu as su accepter un non. Bravo, Amir. J'ai dit d'accord. Oui. Un non, c'est possible. L'étoile reste dans le sable. Le toboggan brille un peu. Tu as fini le chemin ? Oui, papa.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1786,7 +1785,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Olivier range le moule. Papa se lève du banc.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir range le moule étoile. Un peu de sable tombe. Je le secoue. Papa se lève du banc. Le manteau sent encore la pluie. Il est lourd. Oui. On le met sur le bras. Tu prends ma main ? Oui. Ils quittent le bac. Les traces mouillées ont disparu.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1955,12 +1954,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Amir a invité. Il a accepté un non. L'étoile reste dans le bac. Bravo, Amir. On rentre ? Oui. On rentre. L'histoire est finie.</t>
+          <t>Amir a invité. Il a accepté un non. L'étoile reste dans le bac. Bravo, Amir. On rentre ? Oui. On rentre.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir a invité. Il a accepté un non. L'étoile reste dans le bac. Bravo, Amir. On rentre ? Oui. On rentre.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2101,8 +2100,7 @@
 papa|Bravo, Amir.
 enfant-m|On rentre ?
 papa|Oui.
-papa|On rentre.
-narrateur|L'histoire est finie.</t>
+papa|On rentre.</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2168,6 +2166,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.AMI.001-05.xlsx
+++ b/stories/arbres/ATOM-REL.AMI.001-05.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>parc</t>
+          <t>parc, bac à sable</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Olivier, Iris, papa</t>
+          <t>Amir, Mila, papa</t>
         </is>
       </c>
     </row>
